--- a/artfynd/A 23899-2026 artfynd.xlsx
+++ b/artfynd/A 23899-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>58586922</v>
       </c>
       <c r="B2" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667795.9144305582</v>
+        <v>667796</v>
       </c>
       <c r="R2" t="n">
-        <v>6643495.127167867</v>
+        <v>6643495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,19 +758,9 @@
           <t>2015-11-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-11-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -824,12 +809,7 @@
         <v>99673028</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667621.4057706315</v>
+        <v>667621</v>
       </c>
       <c r="R3" t="n">
-        <v>6643569.627564088</v>
+        <v>6643569</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,19 +881,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -956,15 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106175023</v>
+        <v>58589498</v>
       </c>
       <c r="B4" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -972,46 +937,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105336</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>insamlad för uppfödning/kläckning</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vassjön, Tjäderleksmossens NR, Upl</t>
+          <t>Länna gård, 1,9 km NO-ut, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667698.8727163848</v>
+        <v>667787</v>
       </c>
       <c r="R4" t="n">
-        <v>6643670.615382645</v>
+        <v>6643682</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1035,27 +993,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-03-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-11-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>HN07</t>
+          <t>2015-11-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,43 +1007,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>knölticka</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Neoantrodia serialis</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Neoantrodia serialis # Picea abies</t>
+          <t>Horizontal, dead with ground contact</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Henry Åkerström, Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1043,7 @@
         <v>106175010</v>
       </c>
       <c r="B5" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>667641.2678665889</v>
+        <v>667641</v>
       </c>
       <c r="R5" t="n">
-        <v>6643564.497353351</v>
+        <v>6643565</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1188,19 +1117,9 @@
           <t>2022-03-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1253,6 +1172,247 @@
           <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106175023</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>insamlad för uppfödning/kläckning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vassjön, Tjäderleksmossens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>667699</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6643670</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-03-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>HN07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>knölticka</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Fomitopsis serialis</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Fomitopsis serialis # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Insects associated with Amyloporia sinuosa, A. xantha and Neoantrodia serialis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>57250</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>larv</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vassjön S, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>667810</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6643558</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2011-06-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2011-06-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gunnar Carlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunnar Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
